--- a/public/samples/diger-sample-companies.xlsx
+++ b/public/samples/diger-sample-companies.xlsx
@@ -61,7 +61,7 @@
     <t>القاهرة</t>
   </si>
   <si>
-    <t>+20 100 000 0000</t>
+    <t>+201000000000</t>
   </si>
   <si>
     <t>info@company1.example.com</t>
@@ -79,7 +79,7 @@
     <t>الجيزة</t>
   </si>
   <si>
-    <t>+20 100 000 0001</t>
+    <t>+201000000001</t>
   </si>
   <si>
     <t>info@company2.example.com</t>
@@ -94,7 +94,7 @@
     <t>الإسكندرية</t>
   </si>
   <si>
-    <t>+20 100 000 0002</t>
+    <t>+201000000002</t>
   </si>
   <si>
     <t>info@company3.example.com</t>
@@ -106,7 +106,7 @@
     <t>https://company4.example.com</t>
   </si>
   <si>
-    <t>+20 100 000 0003</t>
+    <t>+201000000003</t>
   </si>
   <si>
     <t>info@company4.example.com</t>
@@ -121,7 +121,7 @@
     <t>طنطا</t>
   </si>
   <si>
-    <t>+20 100 000 0004</t>
+    <t>+201000000004</t>
   </si>
   <si>
     <t>info@company5.example.com</t>
@@ -136,7 +136,7 @@
     <t>أسيوط</t>
   </si>
   <si>
-    <t>+20 100 000 0005</t>
+    <t>+201000000005</t>
   </si>
   <si>
     <t>info@company6.example.com</t>

--- a/public/samples/diger-sample-companies.xlsx
+++ b/public/samples/diger-sample-companies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="31">
   <si>
     <t>معرّف السجل</t>
   </si>
@@ -52,9 +52,6 @@
     <t>مقاولات</t>
   </si>
   <si>
-    <t>https://company1.example.com</t>
-  </si>
-  <si>
     <t>غير متاح</t>
   </si>
   <si>
@@ -64,89 +61,56 @@
     <t>+201000000000</t>
   </si>
   <si>
-    <t>info@company1.example.com</t>
-  </si>
-  <si>
     <t>لم يتوفر تأكيد</t>
   </si>
   <si>
     <t>شركة النموذج الثانية</t>
   </si>
   <si>
-    <t>https://company2.example.com</t>
-  </si>
-  <si>
     <t>الجيزة</t>
   </si>
   <si>
     <t>+201000000001</t>
   </si>
   <si>
-    <t>info@company2.example.com</t>
-  </si>
-  <si>
     <t>شركة النموذج الثالثة</t>
   </si>
   <si>
-    <t>https://company3.example.com</t>
-  </si>
-  <si>
     <t>الإسكندرية</t>
   </si>
   <si>
     <t>+201000000002</t>
   </si>
   <si>
-    <t>info@company3.example.com</t>
-  </si>
-  <si>
     <t>شركة النموذج الرابعة</t>
   </si>
   <si>
-    <t>https://company4.example.com</t>
-  </si>
-  <si>
     <t>+201000000003</t>
   </si>
   <si>
-    <t>info@company4.example.com</t>
-  </si>
-  <si>
     <t>شركة النموذج الخامسة</t>
   </si>
   <si>
-    <t>https://company5.example.com</t>
-  </si>
-  <si>
     <t>طنطا</t>
   </si>
   <si>
     <t>+201000000004</t>
   </si>
   <si>
-    <t>info@company5.example.com</t>
-  </si>
-  <si>
     <t>شركة النموذج السادسة</t>
   </si>
   <si>
-    <t>https://company6.example.com</t>
-  </si>
-  <si>
     <t>أسيوط</t>
   </si>
   <si>
     <t>+201000000005</t>
-  </si>
-  <si>
-    <t>info@company6.example.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -158,12 +122,6 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0563C1"/>
-      <sz val="10"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -217,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -228,16 +186,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -645,64 +597,64 @@
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="K2" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>18</v>
+      <c r="I3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -710,69 +662,69 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>18</v>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -780,81 +732,73 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>34</v>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>37</v>
+        <v>13</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>18</v>
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K7"/>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="D4" r:id="rId3"/>
-    <hyperlink ref="D5" r:id="rId4"/>
-    <hyperlink ref="D6" r:id="rId5"/>
-    <hyperlink ref="D7" r:id="rId6"/>
-  </hyperlinks>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/public/samples/diger-sample-companies.xlsx
+++ b/public/samples/diger-sample-companies.xlsx
@@ -11,10 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="31">
-  <si>
-    <t>معرّف السجل</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
   <si>
     <t>اسم الشركة</t>
   </si>
@@ -40,12 +37,6 @@
     <t>البريد المهني</t>
   </si>
   <si>
-    <t>حالة تحقق الهاتف</t>
-  </si>
-  <si>
-    <t>حالة تحقق البريد المهني</t>
-  </si>
-  <si>
     <t>شركة النموذج الأولى</t>
   </si>
   <si>
@@ -59,9 +50,6 @@
   </si>
   <si>
     <t>+201000000000</t>
-  </si>
-  <si>
-    <t>لم يتوفر تأكيد</t>
   </si>
   <si>
     <t>شركة النموذج الثانية</t>
@@ -537,22 +525,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,228 +562,165 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>13</v>
+      <c r="F5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>13</v>
+    <row r="6" ht="24" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="6" t="s">
+    <row r="7" ht="24" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="H7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K7"/>
+  <autoFilter ref="A1:H7"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>